--- a/Defect Report.xlsx
+++ b/Defect Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishanth G\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD9B8061-2E89-491A-9256-AD27838B5727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E6ED18-F899-4279-8DE0-2F3904452E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,18 +132,24 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,31 +187,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,182 +515,182 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="26" style="5" customWidth="1"/>
+    <col min="2" max="2" width="80" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="4">
         <v>46197</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:2" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7"/>
-    </row>
-    <row r="13" spans="1:2" s="9" customFormat="1" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="6"/>
+    </row>
+    <row r="13" spans="1:2" s="1" customFormat="1" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="8"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="7"/>
-    </row>
-    <row r="17" spans="1:2" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="6"/>
+    </row>
+    <row r="17" spans="1:2" s="5" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="7"/>
-    </row>
-    <row r="19" spans="1:2" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="6"/>
+    </row>
+    <row r="19" spans="1:2" s="5" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="B19" s="6"/>
+    </row>
+    <row r="20" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="7"/>
-    </row>
-    <row r="21" spans="1:2" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="6"/>
+    </row>
+    <row r="21" spans="1:2" s="5" customFormat="1" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="B21" s="6"/>
+    </row>
+    <row r="22" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="7"/>
-    </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="6"/>
+    </row>
+    <row r="23" spans="1:2" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
